--- a/cet4/result/74_穿越才女_文学女神的逆袭路/74_穿越才女_文学女神的逆袭路_学习版.xlsx
+++ b/cet4/result/74_穿越才女_文学女神的逆袭路/74_穿越才女_文学女神的逆袭路_学习版.xlsx
@@ -397,941 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>April</v>
       </c>
       <c r="B2" t="str">
-        <v>April</v>
+        <v>/ˈeɪprəl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>四月</v>
       </c>
-      <c r="D2" t="str">
-        <v>April(四月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>literary</v>
       </c>
       <c r="B3" t="str">
-        <v>literary</v>
+        <v>/ˈlɪtəreri/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>文学的</v>
       </c>
-      <c r="D3" t="str">
-        <v>literary(文学的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>text</v>
       </c>
       <c r="B4" t="str">
-        <v>text</v>
+        <v>/tekst/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>课文</v>
       </c>
-      <c r="D4" t="str">
-        <v>text(课文)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>surround</v>
       </c>
       <c r="B5" t="str">
-        <v>surround</v>
+        <v>/səˈraʊnd/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>围绕</v>
       </c>
-      <c r="D5" t="str">
-        <v>surround(围绕)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>instantly</v>
       </c>
       <c r="B6" t="str">
-        <v>instantly</v>
+        <v>/ˈɪnstəntli/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>立即</v>
       </c>
-      <c r="D6" t="str">
-        <v>instantly(立即)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>headache</v>
       </c>
       <c r="B7" t="str">
-        <v>headache</v>
+        <v>/ˈhedeɪk/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>头痛</v>
       </c>
-      <c r="D7" t="str">
-        <v>headache(头痛)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>prince</v>
       </c>
       <c r="B8" t="str">
-        <v>prince</v>
+        <v>/prɪns/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>王子</v>
       </c>
-      <c r="D8" t="str">
-        <v>prince(王子)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>clever</v>
       </c>
       <c r="B9" t="str">
-        <v>clever</v>
+        <v>/ˈklevər/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>聪明的</v>
       </c>
-      <c r="D9" t="str">
-        <v>clever(聪明的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>look</v>
       </c>
       <c r="B10" t="str">
-        <v>look</v>
+        <v>/lʊk/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>看</v>
       </c>
-      <c r="D10" t="str">
-        <v>look(看)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>draw</v>
       </c>
       <c r="B11" t="str">
-        <v>draw</v>
+        <v>/drɔː/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>画</v>
       </c>
-      <c r="D11" t="str">
-        <v>draw(画)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>possibility</v>
       </c>
       <c r="B12" t="str">
-        <v>possibility</v>
+        <v>/ˌpɑːsəˈbɪləti/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>可能性</v>
       </c>
-      <c r="D12" t="str">
-        <v>possibility(可能性)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>landlord</v>
       </c>
       <c r="B13" t="str">
-        <v>landlord</v>
+        <v>/ˈlændlɔːrd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>房东</v>
       </c>
-      <c r="D13" t="str">
-        <v>landlord(房东)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>mug</v>
       </c>
       <c r="B14" t="str">
-        <v>mug</v>
+        <v>/mʌɡ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>杯子</v>
       </c>
-      <c r="D14" t="str">
-        <v>mug(杯子)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>lantern</v>
       </c>
       <c r="B15" t="str">
-        <v>lantern</v>
+        <v>/ˈlæntərn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>灯笼</v>
       </c>
-      <c r="D15" t="str">
-        <v>lantern(灯笼)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>recollect</v>
       </c>
       <c r="B16" t="str">
-        <v>recollect</v>
+        <v>/ˌrekəˈlekt/</v>
       </c>
       <c r="C16" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D16" t="str">
         <v>回忆</v>
       </c>
-      <c r="D16" t="str">
-        <v>recollect(回忆)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>cry</v>
       </c>
       <c r="B17" t="str">
-        <v>cry</v>
+        <v>/kraɪ/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vi./v.</v>
+      </c>
+      <c r="D17" t="str">
         <v>哭</v>
       </c>
-      <c r="D17" t="str">
-        <v>cry(哭)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>rumour</v>
       </c>
       <c r="B18" t="str">
-        <v>rumour</v>
+        <v>/ˈruːmər/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>谣言</v>
       </c>
-      <c r="D18" t="str">
-        <v>rumour(谣言)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>effective</v>
       </c>
       <c r="B19" t="str">
-        <v>effective</v>
+        <v>/ɪˈfektɪv/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>有效的</v>
       </c>
-      <c r="D19" t="str">
-        <v>effective(有效的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>solution</v>
       </c>
       <c r="B20" t="str">
-        <v>solution</v>
+        <v>/səˈluːʃn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>解决方案</v>
       </c>
-      <c r="D20" t="str">
-        <v>solution(解决方案)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>anyhow</v>
       </c>
       <c r="B21" t="str">
-        <v>anyhow</v>
+        <v>/ˈenihaʊ/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>无论如何</v>
       </c>
-      <c r="D21" t="str">
-        <v>anyhow(无论如何)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>basic</v>
       </c>
       <c r="B22" t="str">
-        <v>basic</v>
+        <v>/ˈbeɪsɪk/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>基础的</v>
       </c>
-      <c r="D22" t="str">
-        <v>basic(基础的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>thereby</v>
       </c>
       <c r="B23" t="str">
-        <v>literary</v>
+        <v>/ˌðerˈbaɪ/</v>
       </c>
       <c r="C23" t="str">
-        <v>文学的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D23" t="str">
-        <v>literary(文学的)📢</v>
+        <v>从而</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>classify</v>
       </c>
       <c r="B24" t="str">
-        <v>thereby</v>
+        <v>/ˈklæsɪfaɪ/</v>
       </c>
       <c r="C24" t="str">
-        <v>从而</v>
+        <v>vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>thereby(从而)📢</v>
+        <v>分类</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>up</v>
       </c>
       <c r="B25" t="str">
-        <v>classify</v>
+        <v>/ʌp/</v>
       </c>
       <c r="C25" t="str">
-        <v>分类</v>
+        <v>v./adj./adv./prep.</v>
       </c>
       <c r="D25" t="str">
-        <v>classify(分类)📢</v>
+        <v>向上</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>hatred</v>
       </c>
       <c r="B26" t="str">
-        <v>up</v>
+        <v>/ˈheɪtrɪd/</v>
       </c>
       <c r="C26" t="str">
-        <v>向上</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>up(向上)📢</v>
+        <v>憎恨</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>dismiss</v>
       </c>
       <c r="B27" t="str">
-        <v>hatred</v>
+        <v>/dɪsˈmɪs/</v>
       </c>
       <c r="C27" t="str">
-        <v>憎恨</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>hatred(憎恨)📢</v>
+        <v>解雇</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>enemy</v>
       </c>
       <c r="B28" t="str">
-        <v>dismiss</v>
+        <v>/ˈenəmi/</v>
       </c>
       <c r="C28" t="str">
-        <v>解雇</v>
+        <v>n./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>dismiss(解雇)📢</v>
+        <v>敌人</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>resist</v>
       </c>
       <c r="B29" t="str">
-        <v>enemy</v>
+        <v>/rɪˈzɪst/</v>
       </c>
       <c r="C29" t="str">
-        <v>敌人</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>enemy(敌人)📢</v>
+        <v>抵抗</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>listener</v>
       </c>
       <c r="B30" t="str">
-        <v>resist</v>
+        <v>/ˈlɪsənər/</v>
       </c>
       <c r="C30" t="str">
-        <v>抵抗</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>resist(抵抗)📢</v>
+        <v>倾听者</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>midst</v>
       </c>
       <c r="B31" t="str">
-        <v>literary</v>
+        <v>/mɪdst/</v>
       </c>
       <c r="C31" t="str">
-        <v>文学的</v>
+        <v>n./prep.</v>
       </c>
       <c r="D31" t="str">
-        <v>literary(文学的)📢</v>
+        <v>中间</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>affection</v>
       </c>
       <c r="B32" t="str">
-        <v>listener</v>
+        <v>/əˈfekʃn/</v>
       </c>
       <c r="C32" t="str">
-        <v>倾听者</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>listener(倾听者)📢</v>
+        <v>感情</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>supermarket</v>
       </c>
       <c r="B33" t="str">
-        <v>midst</v>
+        <v>/ˈsuːpərmɑːrkɪt/</v>
       </c>
       <c r="C33" t="str">
-        <v>中间</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>midst(中间)📢</v>
+        <v>超市</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>install</v>
       </c>
       <c r="B34" t="str">
-        <v>affection</v>
+        <v>/ɪnˈstɔːl/</v>
       </c>
       <c r="C34" t="str">
-        <v>感情</v>
+        <v>vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>affection(感情)📢</v>
+        <v>安装</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>lessen</v>
       </c>
       <c r="B35" t="str">
-        <v>clever</v>
+        <v>/ˈlesn/</v>
       </c>
       <c r="C35" t="str">
-        <v>聪明的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>clever(聪明的)📢</v>
+        <v>减少</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>union</v>
       </c>
       <c r="B36" t="str">
-        <v>supermarket</v>
+        <v>/ˈjuːniən/</v>
       </c>
       <c r="C36" t="str">
-        <v>超市</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>supermarket(超市)📢</v>
+        <v>联盟</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>ambition</v>
       </c>
       <c r="B37" t="str">
-        <v>install</v>
+        <v>/æmˈbɪʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>安装</v>
+        <v>n./vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>install(安装)📢</v>
+        <v>雄心</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>wherever</v>
       </c>
       <c r="B38" t="str">
-        <v>lessen</v>
+        <v>/werˈevər/</v>
       </c>
       <c r="C38" t="str">
-        <v>减少</v>
+        <v>v./adv./conj.</v>
       </c>
       <c r="D38" t="str">
-        <v>lessen(减少)📢</v>
+        <v>无论在哪里</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>foundation</v>
       </c>
       <c r="B39" t="str">
-        <v>dismiss</v>
+        <v>/faʊnˈdeɪʃn/</v>
       </c>
       <c r="C39" t="str">
-        <v>解雇</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>dismiss(解雇)📢</v>
+        <v>基础</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>insure</v>
       </c>
       <c r="B40" t="str">
-        <v>headache</v>
+        <v>/ɪnˈʃʊr/</v>
       </c>
       <c r="C40" t="str">
-        <v>头痛</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>headache(头痛)📢</v>
+        <v>确保</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>interval</v>
       </c>
       <c r="B41" t="str">
-        <v>union</v>
+        <v>/ˈɪntərvl/</v>
       </c>
       <c r="C41" t="str">
-        <v>联盟</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>union(联盟)📢</v>
+        <v>间隔</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>drum</v>
       </c>
       <c r="B42" t="str">
-        <v>ambition</v>
+        <v>/drʌm/</v>
       </c>
       <c r="C42" t="str">
-        <v>雄心</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>ambition(雄心)📢</v>
+        <v>鼓</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>mushroom</v>
       </c>
       <c r="B43" t="str">
-        <v>wherever</v>
+        <v>/ˈmʌʃrʊm,ˈmʌʃruːm/</v>
       </c>
       <c r="C43" t="str">
-        <v>无论在哪里</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>wherever(无论在哪里)📢</v>
+        <v>蘑菇</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>photograph</v>
       </c>
       <c r="B44" t="str">
-        <v>thereby</v>
+        <v>/ˈfoʊtəɡræf/</v>
       </c>
       <c r="C44" t="str">
-        <v>从而</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>thereby(从而)📢</v>
+        <v>照片</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>deed</v>
       </c>
       <c r="B45" t="str">
-        <v>effective</v>
+        <v>/diːd/</v>
       </c>
       <c r="C45" t="str">
-        <v>有效的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D45" t="str">
-        <v>effective(有效的)📢</v>
+        <v>行动</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>round</v>
       </c>
       <c r="B46" t="str">
-        <v>foundation</v>
+        <v>/raʊnd/</v>
       </c>
       <c r="C46" t="str">
-        <v>基础</v>
+        <v>n./vt./vi./v./adj./adv./prep.</v>
       </c>
       <c r="D46" t="str">
-        <v>foundation(基础)📢</v>
+        <v>圆的</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>return</v>
       </c>
       <c r="B47" t="str">
-        <v>insure</v>
+        <v>/rɪˈtɜːrn/</v>
       </c>
       <c r="C47" t="str">
-        <v>确保</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>insure(确保)📢</v>
+        <v>返回</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>nap</v>
       </c>
       <c r="B48" t="str">
-        <v>interval</v>
+        <v>/næp/</v>
       </c>
       <c r="C48" t="str">
-        <v>间隔</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>interval(间隔)📢</v>
+        <v>小睡</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>tape</v>
       </c>
       <c r="B49" t="str">
-        <v>drum</v>
+        <v>/teɪp/</v>
       </c>
       <c r="C49" t="str">
-        <v>鼓</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>drum(鼓)📢</v>
+        <v>磁带</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>freeze</v>
       </c>
       <c r="B50" t="str">
-        <v>mushroom</v>
+        <v>/friːz/</v>
       </c>
       <c r="C50" t="str">
-        <v>蘑菇</v>
+        <v>v.</v>
       </c>
       <c r="D50" t="str">
-        <v>mushroom(蘑菇)📢</v>
+        <v>结冰</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>run</v>
       </c>
       <c r="B51" t="str">
-        <v>photograph</v>
+        <v>/rʌn/</v>
       </c>
       <c r="C51" t="str">
-        <v>照片</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>photograph(照片)📢</v>
+        <v>奔跑</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>bathe</v>
       </c>
       <c r="B52" t="str">
-        <v>affection</v>
+        <v>/beɪð/</v>
       </c>
       <c r="C52" t="str">
-        <v>感情</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D52" t="str">
-        <v>affection(感情)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>ambition</v>
-      </c>
-      <c r="C53" t="str">
-        <v>雄心</v>
-      </c>
-      <c r="D53" t="str">
-        <v>ambition(雄心)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>deed</v>
-      </c>
-      <c r="C54" t="str">
-        <v>行动</v>
-      </c>
-      <c r="D54" t="str">
-        <v>deed(行动)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>round</v>
-      </c>
-      <c r="C55" t="str">
-        <v>圆的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>round(圆的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>photograph</v>
-      </c>
-      <c r="C56" t="str">
-        <v>照片</v>
-      </c>
-      <c r="D56" t="str">
-        <v>photograph(照片)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>return</v>
-      </c>
-      <c r="C57" t="str">
-        <v>返回</v>
-      </c>
-      <c r="D57" t="str">
-        <v>return(返回)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>nap</v>
-      </c>
-      <c r="C58" t="str">
-        <v>小睡</v>
-      </c>
-      <c r="D58" t="str">
-        <v>nap(小睡)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>tape</v>
-      </c>
-      <c r="C59" t="str">
-        <v>磁带</v>
-      </c>
-      <c r="D59" t="str">
-        <v>tape(磁带)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>freeze</v>
-      </c>
-      <c r="C60" t="str">
-        <v>结冰</v>
-      </c>
-      <c r="D60" t="str">
-        <v>freeze(结冰)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>wherever</v>
-      </c>
-      <c r="C61" t="str">
-        <v>无论在哪里</v>
-      </c>
-      <c r="D61" t="str">
-        <v>wherever(无论在哪里)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>run</v>
-      </c>
-      <c r="C62" t="str">
-        <v>奔跑</v>
-      </c>
-      <c r="D62" t="str">
-        <v>run(奔跑)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>bathe</v>
-      </c>
-      <c r="C63" t="str">
         <v>沐浴</v>
-      </c>
-      <c r="D63" t="str">
-        <v>bathe(沐浴)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>literary</v>
-      </c>
-      <c r="C64" t="str">
-        <v>文学的</v>
-      </c>
-      <c r="D64" t="str">
-        <v>literary(文学的)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>photograph</v>
-      </c>
-      <c r="C65" t="str">
-        <v>照片</v>
-      </c>
-      <c r="D65" t="str">
-        <v>photograph(照片)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>deed</v>
-      </c>
-      <c r="C66" t="str">
-        <v>证书</v>
-      </c>
-      <c r="D66" t="str">
-        <v>deed(证书)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>